--- a/report/statistical_report.xlsx
+++ b/report/statistical_report.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated by</t>
+          <t>Build script</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/report/statistical_report.xlsx
+++ b/report/statistical_report.xlsx
@@ -11,23 +11,23 @@
     <sheet name="Fig4_frequency_metrics" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Fig4_transition_metrics" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Fig4_bout_duration" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="fig4_bout_cluster_per_animal" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="fig4_bout_overall_per_animal" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="fig4_diversity_per_animal" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="fig4_transition_per_animal" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="fig5_timecourse_mixedlm" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="fig5c_correct_report" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="fig5c_frequency_gee" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="fig5c_ms_vs_correct" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="fig6_bout_resilience_stats" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="fig6_diversity_resilience_stats" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="fig6_transition_resilience_stat" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="gee_freq_results" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="stats_fig3_overtime" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="stats_fig3A_GEE" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="stats_fig4_bouts_mixedlm" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="stats_fig4_diversity_mixedlm" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="stats_fig4_diversity_OLS" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="fig3_frequency_gee_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="fig4_bout_cluster_per_animal" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="fig4_bout_overall_per_animal" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="fig4_diversity_per_animal" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="fig4_transition_per_animal" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="fig5_timecourse_mixedlm" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="fig5c_frequency_contrast_audit" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="fig5c_frequency_contrasts" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="fig5c_frequency_gee" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="fig6_bout_resilience_stats" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="fig6_diversity_resilience_stats" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="fig6_transition_resilience_stat" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="ms_consistency_audit" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="stats_fig3_overtime" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="stats_fig3A_GEE" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="stats_fig4_bouts_mixedlm" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="stats_fig4_diversity_mixedlm" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="stats_fig4_transition_mixedlm" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>results/statistics</t>
+          <t>statistics</t>
         </is>
       </c>
     </row>
@@ -542,18 +542,6 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>Mustard fill marks p &lt; 0.05 in p-value columns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Manuscript text audit</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>results/statistics/manuscript_results_text.md</t>
         </is>
       </c>
     </row>
@@ -568,16 +556,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="57" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,894 +576,1603 @@
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>Parameter</t>
+          <t>panel</t>
         </is>
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
-          <t>Coef.</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t>Std. Err.</t>
+          <t>coef</t>
         </is>
       </c>
       <c r="E1" s="6" t="inlineStr">
         <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
           <t>z</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>P&gt;|z|</t>
-        </is>
-      </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
-          <t>P_BH_FDR</t>
+          <t>p</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Freezing</t>
+          <t>Freeze</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>7.5136</v>
-      </c>
       <c r="D2" t="n">
-        <v>0.0926</v>
+        <v>1.167734739514446e-19</v>
       </c>
       <c r="E2" t="n">
-        <v>81.10809999999999</v>
+        <v>57937066.35940005</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>2.015522726454005e-27</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Freezing</t>
+          <t>Freeze</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Control/ELS</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.3417</v>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.Control]</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>0.082</v>
+        <v>1.983764337921433e-18</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.1685</v>
+        <v>47222751.81826599</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>4.200865602995425e-26</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Freezing</t>
+          <t>Freeze</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Control/Resilient</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.06710000000000001</v>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1111</v>
+        <v>1.59747688188722e-17</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6038</v>
+        <v>96124105.99966487</v>
       </c>
       <c r="F4" t="n">
-        <v>0.546</v>
+        <v>1.661889975749464e-25</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Freezing</t>
+          <t>Freeze</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ELS/Resilient</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.4088</v>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C(experiment)[T.3]</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1176</v>
+        <v>5.430008571821657e-20</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4759</v>
+        <v>54258354.96999358</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>0.0018</v>
+        <v>1.00076911193209e-27</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Freezing</t>
+          <t>Freeze</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Experiment</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.1804</v>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>time_bin_numeric</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>0.0385</v>
+        <v>0.0847285166940339</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6811</v>
+        <v>0.0043413334057078</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>19.51670345858133</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>7.918530004551611e-85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sniffing</t>
+          <t>Freeze</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4.8738</v>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.Control]:time_bin_numeric</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2642</v>
+        <v>0.0415235158262912</v>
       </c>
       <c r="E7" t="n">
-        <v>18.4459</v>
+        <v>0.005672574805247</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>7.320047289263159</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>2.478835867593613e-13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sniffing</t>
+          <t>Freeze</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Control/ELS</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.7107</v>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]:time_bin_numeric</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2475</v>
+        <v>0.0621669859514687</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8719</v>
+        <v>0.008024619437083</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0041</v>
+        <v>7.747032297156085</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>9.406503761765563e-15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sniffing</t>
+          <t>Freeze</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Control/Resilient</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.3637</v>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Group Var</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>0.3137</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.1593</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.2463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sniffing</t>
+          <t>Sniff</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ELS/Resilient</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.3471</v>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3126</v>
+        <v>-3.578632558552098e-20</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1103</v>
+        <v>30711290.43649872</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2669</v>
+        <v>-1.165249817799608e-27</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4694</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sniffing</t>
+          <t>Sniff</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Experiment</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.4918</v>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.Control]</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1188</v>
+        <v>5.568326604626117e-18</v>
       </c>
       <c r="E11" t="n">
-        <v>4.1392</v>
+        <v>47691063.63991545</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1.167582808944873e-25</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Grooming</t>
+          <t>Sniff</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2.7854</v>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>0.2699</v>
+        <v>6.617483125559545e-18</v>
       </c>
       <c r="E12" t="n">
-        <v>10.3191</v>
+        <v>69970892.32654329</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>9.457479968494296e-26</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Grooming</t>
+          <t>Sniff</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Control/ELS</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.0912</v>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>C(experiment)[T.3]</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>0.3879</v>
+        <v>-9.98932096343714e-21</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2351</v>
+        <v>18092547.81131582</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8141</v>
+        <v>-5.521235078450038e-28</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Grooming</t>
+          <t>Sniff</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Control/Resilient</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.0152</v>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>time_bin_numeric</t>
+        </is>
       </c>
       <c r="D14" t="n">
-        <v>0.4717</v>
+        <v>-0.0253902572523262</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0322</v>
+        <v>0.0030708557776315</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9743000000000001</v>
+        <v>-8.268137317705328</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>1.360681196832254e-16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Grooming</t>
+          <t>Sniff</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ELS/Resilient</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.076</v>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.Control]:time_bin_numeric</t>
+        </is>
       </c>
       <c r="D15" t="n">
-        <v>0.5192</v>
+        <v>0.0171463548133018</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1463</v>
+        <v>0.0040125135498317</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8837</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.8904</v>
+        <v>4.273220414176795</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>1.92669829275846e-05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Grooming</t>
+          <t>Sniff</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Experiment</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.3976</v>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]:time_bin_numeric</t>
+        </is>
       </c>
       <c r="D16" t="n">
-        <v>0.1873</v>
+        <v>0.0112817916438606</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.1223</v>
+        <v>0.0056762396846234</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0338</v>
+        <v>1.987546733521882</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0.0468618424244712</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Turn</t>
+          <t>Sniff</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>8.4549</v>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Group Var</t>
+        </is>
       </c>
       <c r="D17" t="n">
-        <v>0.0386</v>
-      </c>
-      <c r="E17" t="n">
-        <v>219.1722</v>
-      </c>
-      <c r="F17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Turn</t>
+          <t>Groom</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Control/ELS</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.1408</v>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
       </c>
       <c r="D18" t="n">
-        <v>0.0341</v>
+        <v>8.730431564512796e-23</v>
       </c>
       <c r="E18" t="n">
-        <v>4.1325</v>
+        <v>578778.7694682108</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.508422911319713e-28</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Turn</t>
+          <t>Groom</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Control/Resilient</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.0037</v>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.Control]</t>
+        </is>
       </c>
       <c r="D19" t="n">
-        <v>0.0341</v>
+        <v>-3.303675330007019e-20</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.11</v>
+        <v>799094.3650951521</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9124</v>
+        <v>-4.134274341446063e-26</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Turn</t>
+          <t>Groom</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ELS/Resilient</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.1445</v>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]</t>
+        </is>
       </c>
       <c r="D20" t="n">
-        <v>0.0326</v>
+        <v>-8.402347656431446e-20</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.4375</v>
+        <v>2030758.645158524</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>0.0001</v>
+        <v>-4.137541246697757e-26</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Turn</t>
+          <t>Groom</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Experiment</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.0094</v>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>C(experiment)[T.3]</t>
+        </is>
       </c>
       <c r="D21" t="n">
-        <v>0.0166</v>
+        <v>-1.289751086399553e-23</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5679</v>
+        <v>1231877.14494184</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5701000000000001</v>
+        <v>-1.046980286707442e-29</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Locomotion</t>
+          <t>Groom</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>7.0792</v>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>time_bin_numeric</t>
+        </is>
       </c>
       <c r="D22" t="n">
-        <v>0.1455</v>
+        <v>5.911330049261086e-05</v>
       </c>
       <c r="E22" t="n">
-        <v>48.6491</v>
+        <v>9.018022514846688e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.6555018064691073</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5121447237052608</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Locomotion</t>
+          <t>Groom</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Control/ELS</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.2461</v>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.Control]:time_bin_numeric</t>
+        </is>
       </c>
       <c r="D23" t="n">
-        <v>0.1624</v>
+        <v>-8.698786495254115e-05</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5157</v>
+        <v>0.0001178333993966</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1296</v>
+        <v>-0.7382275772231575</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.4603761675161169</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Locomotion</t>
+          <t>Groom</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Control/Resilient</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.0252</v>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]:time_bin_numeric</t>
+        </is>
       </c>
       <c r="D24" t="n">
-        <v>0.2564</v>
+        <v>-0.0002297482211275</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0983</v>
+        <v>0.0001666911798608</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9217</v>
+        <v>-1.378286609521128</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1681148158077938</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Locomotion</t>
+          <t>Groom</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ELS/Resilient</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.2713</v>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Group Var</t>
+        </is>
       </c>
       <c r="D25" t="n">
-        <v>0.2451</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1.1072</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.2682</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.4694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Locomotion</t>
+          <t>Turn</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Experiment</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.4245</v>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
       </c>
       <c r="D26" t="n">
-        <v>0.0893</v>
+        <v>6.407143061156887e-21</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.7546</v>
+        <v>54965824.70530519</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1.165659406641902e-28</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Climbing</t>
+          <t>Turn</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>6.3372</v>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.Control]</t>
+        </is>
       </c>
       <c r="D27" t="n">
-        <v>0.1394</v>
+        <v>-9.767338664955905e-18</v>
       </c>
       <c r="E27" t="n">
-        <v>45.4693</v>
+        <v>90584380.01758012</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-1.078258598564158e-25</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Climbing</t>
+          <t>Turn</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Control/ELS</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.0488</v>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]</t>
+        </is>
       </c>
       <c r="D28" t="n">
-        <v>0.1457</v>
+        <v>-2.019034610743105e-17</v>
       </c>
       <c r="E28" t="n">
-        <v>0.335</v>
+        <v>121906486.7650236</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7377</v>
+        <v>-1.656215894921836e-25</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Climbing</t>
+          <t>Turn</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Control/Resilient</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.0092</v>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>C(experiment)[T.3]</t>
+        </is>
       </c>
       <c r="D29" t="n">
-        <v>0.2737</v>
+        <v>-9.027860363729511e-21</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0337</v>
+        <v>85757026.40332018</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9731</v>
+        <v>-1.052725443308979e-28</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Climbing</t>
+          <t>Turn</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ELS/Resilient</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.0396</v>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>time_bin_numeric</t>
+        </is>
       </c>
       <c r="D30" t="n">
-        <v>0.2871</v>
+        <v>0.0036431308155446</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1378</v>
+        <v>0.0056886486120862</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8904</v>
+        <v>0.6404211375974876</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8904</v>
+        <v>0.5218988444059371</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Climbing</t>
+          <t>Turn</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Experiment</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.1956</v>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.Control]:time_bin_numeric</t>
+        </is>
       </c>
       <c r="D31" t="n">
-        <v>0.0745</v>
+        <v>-0.0413771610129894</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.6239</v>
+        <v>0.007433035378116</v>
       </c>
       <c r="F31" t="n">
-        <v>0.008699999999999999</v>
+        <v>-5.56665734900303</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>2.596723010716253e-08</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jump</t>
+          <t>Turn</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>4.4057</v>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]:time_bin_numeric</t>
+        </is>
       </c>
       <c r="D32" t="n">
-        <v>0.1181</v>
+        <v>-0.0540584747308885</v>
       </c>
       <c r="E32" t="n">
-        <v>37.3104</v>
+        <v>0.0105150275174129</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-5.1410683083204</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>2.731807052640286e-07</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jump</t>
+          <t>Turn</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Control/ELS</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0.0407</v>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Group Var</t>
+        </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1212</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.3359</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.7369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jump</t>
+          <t>Locomotion</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Control/Resilient</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.0519</v>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
       </c>
       <c r="D34" t="n">
-        <v>0.1613</v>
+        <v>-2.563198223044489e-20</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.322</v>
+        <v>20149826.89930953</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7475000000000001</v>
+        <v>-1.272069599333542e-27</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jump</t>
+          <t>Locomotion</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ELS/Resilient</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.0927</v>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.Control]</t>
+        </is>
       </c>
       <c r="D35" t="n">
-        <v>0.1726</v>
+        <v>5.948582117017596e-19</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5368000000000001</v>
+        <v>26827188.95559184</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5914</v>
+        <v>2.217370640980884e-26</v>
       </c>
       <c r="G35" t="n">
-        <v>0.828</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Locomotion</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>-6.59350385538885e-20</v>
+      </c>
+      <c r="E36" t="n">
+        <v>39407904.2365334</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-1.673142478172258e-27</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Locomotion</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>C(experiment)[T.3]</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>-1.002492387846058e-20</v>
+      </c>
+      <c r="E37" t="n">
+        <v>21438700.53821893</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-4.676087461825903e-28</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Locomotion</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>time_bin_numeric</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.0184532019704433</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.0017401956340854</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-10.60409623435292</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>2.852080397105039e-26</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Locomotion</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.Control]:time_bin_numeric</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.0064833059660645</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.0022738152055162</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-2.851289739964851</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>0.0043542272933309</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Locomotion</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]:time_bin_numeric</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.0034568509396095</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.0032166172013532</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-1.074685212202201</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.2825156866283029</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Locomotion</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Group Var</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Climb</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>6.949261310959979</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.5821771162369743</v>
+      </c>
+      <c r="F42" t="n">
+        <v>11.93667891977275</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>7.620559102456307e-33</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Climb</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.Control]</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.4525802160234881</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7283750981233754</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.6213559705562971</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.534365434848195</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Climb</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>-0.0131287063642658</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.03270070912007</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.0127129828113049</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.9898567805182504</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Climb</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>C(experiment)[T.3]</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>-1.282080024006236</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.4894079502557587</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-2.619655081892797</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>0.0088018741711899</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Climb</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>time_bin_numeric</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>-0.0132233169129719</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.0018502951375046</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-7.146598747919252</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>8.895440574442136e-13</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Climb</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.Control]:time_bin_numeric</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>-0.0024445111938805</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.0024176759991481</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-1.011099582715724</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.3119687700804534</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Climb</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]:time_bin_numeric</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>-0.0004287994891444</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.0034201276283545</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.125375288801941</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.9002264504128519</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Climb</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Group Var</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.118172825197827</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.0266040885179105</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4.44190467635342</v>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>8.916606238198319e-06</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>Jump</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Experiment</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.034</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.0613</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-0.554</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.5795</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2.873196023389088e-21</v>
+      </c>
+      <c r="E50" t="n">
+        <v>5999080.844399334</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.789393738661594e-28</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.Control]</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>-2.541163907958393e-19</v>
+      </c>
+      <c r="E51" t="n">
+        <v>6017900.438476866</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-4.222675223589379e-26</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-2.777725951462236e-19</v>
+      </c>
+      <c r="E52" t="n">
+        <v>5666649.246303425</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-4.901884395393369e-26</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>C(experiment)[T.3]</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>9.550301325054638e-22</v>
+      </c>
+      <c r="E53" t="n">
+        <v>6274587.774688235</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.522060359659111e-28</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>time_bin_numeric</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.0020530925013683</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.0004566247318219</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4.496235876616957</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>6.91670039181544e-06</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.Control]:time_bin_numeric</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.0002791861908766</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.0005966457093067</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-0.4679262525847488</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.6398373289510549</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]:time_bin_numeric</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>-0.0003163200145958</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.000844035543</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-0.3747709645870242</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.7078308099381875</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Group Var</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1484,633 +2181,6 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>cluster</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>contrast</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>beta</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>z</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>significant</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Control/ELS</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.3416478079282853</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.08198848478430119</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-4.167021854680041</v>
-      </c>
-      <c r="F2" s="7" t="n">
-        <v>3.086049215065118e-05</v>
-      </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Control/Resilient</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.0670186109510118</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.1110629287165263</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.6034291705206886</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.5462232214655676</v>
-      </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ELS/Resilient</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.4086664188792971</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1176001401377532</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3.475050441271564</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>0.0005107573006136</v>
-      </c>
-      <c r="G4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Sniff</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Control/ELS</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.7122644066487785</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.2476069428918566</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2.876593032206948</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>0.0040199367747777</v>
-      </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sniff</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Control/Resilient</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.363075390529554</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.3138676536064639</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.156778617859068</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.2473628198779007</v>
-      </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sniff</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ELS/Resilient</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.3491890161192245</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.3124160673577382</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-1.117705049783431</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.2636929853268198</v>
-      </c>
-      <c r="G7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Groom</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Control/ELS</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.0657920068416422</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.4237538768871108</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.1552599526049161</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.8766163859000841</v>
-      </c>
-      <c r="G8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Groom</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Control/Resilient</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.1565270307442328</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.5310732375744608</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.294737184383701</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.76819465525537</v>
-      </c>
-      <c r="G9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Groom</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ELS/Resilient</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0907350239025905</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.5918401476246433</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.1533100183668792</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.8781538005582127</v>
-      </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Turn</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Control/ELS</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.1407695611938317</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.0340640495018712</v>
-      </c>
-      <c r="E11" t="n">
-        <v>4.132496378215362</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>3.588444230979757e-05</v>
-      </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Turn</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Control/Resilient</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.0037471788166275</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.034077248792987</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.1099613070113432</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.9124400613039352</v>
-      </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Turn</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ELS/Resilient</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.1445167400104587</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0325680545474696</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-4.437377117500765</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>9.106167537030892e-06</v>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Locomotion</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Control/ELS</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.2426275308278193</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.1615453482112258</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1.501915923388743</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.1331188237189243</v>
-      </c>
-      <c r="G14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Locomotion</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Control/Resilient</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.0218368633282987</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.2551261072049063</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.0855924294363192</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.9317904168091666</v>
-      </c>
-      <c r="G15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Locomotion</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ELS/Resilient</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.2644643941561181</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.2442338923042543</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.082832491678352</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.2788827807889146</v>
-      </c>
-      <c r="G16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Climb</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Control/ELS</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.0146566202937246</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.1494183646225211</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.09809115720649191</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.921859909190788</v>
-      </c>
-      <c r="G17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Climb</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Control/Resilient</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.0057322879042903</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.272052617366275</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.0210705118729763</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.983189407787424</v>
-      </c>
-      <c r="G18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Climb</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ELS/Resilient</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.0089243323894344</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.2872855372931595</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-0.0310643287981726</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.975218237426922</v>
-      </c>
-      <c r="G19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Jump</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Control/ELS</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.0267473249112214</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.1296989066103411</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.2062262945020755</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.8366141492357301</v>
-      </c>
-      <c r="G20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Jump</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Control/Resilient</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.0206137995032985</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.1654846315888874</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-0.1245662470609918</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.900866951158532</v>
-      </c>
-      <c r="G21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Jump</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ELS/Resilient</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.0473611244145201</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.1788745472574913</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-0.2647728541632224</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.7911844500072999</v>
-      </c>
-      <c r="G22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2705,7 +2775,1555 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Coef.</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Std. Err.</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>P&gt;|z|</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>P_BH_FDR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Freezing</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>7.5136</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0926</v>
+      </c>
+      <c r="E2" t="n">
+        <v>81.10809999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Freezing</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Control/ELS</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.3417</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-4.1685</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Freezing</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Control/Resilient</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.06710000000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.6038</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.546</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Freezing</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ELS/Resilient</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.4759</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>0.0018</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Freezing</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Experiment</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1804</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.6811</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sniffing</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4.8738</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2642</v>
+      </c>
+      <c r="E7" t="n">
+        <v>18.4459</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sniffing</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Control/ELS</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.7107</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2475</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.8719</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0041</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sniffing</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Control/Resilient</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.1593</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2463</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sniffing</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ELS/Resilient</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.3471</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.1103</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2669</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4694</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sniffing</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Experiment</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.4918</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1188</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.1392</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Grooming</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2.7854</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2699</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10.3191</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Grooming</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Control/ELS</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.0912</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.3879</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.2351</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8141</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Grooming</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Control/Resilient</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.0152</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4717</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.0322</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9743000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Grooming</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ELS/Resilient</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5192</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.1463</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.8837</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8904</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Grooming</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Experiment</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.3976</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1873</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-2.1223</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.0338</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>8.4549</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="E17" t="n">
+        <v>219.1722</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Control/ELS</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.1408</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0341</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4.1325</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Control/Resilient</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.0341</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9124</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ELS/Resilient</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.1445</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-4.4375</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Experiment</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5679</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5701000000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Locomotion</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>7.0792</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="E22" t="n">
+        <v>48.6491</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Locomotion</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Control/ELS</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.2461</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.1624</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-1.5157</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.1296</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Locomotion</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Control/Resilient</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.2564</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9217</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Locomotion</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ELS/Resilient</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.2713</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.2451</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.1072</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.2682</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.4694</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Locomotion</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Experiment</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.4245</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0893</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-4.7546</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Climbing</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>6.3372</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1394</v>
+      </c>
+      <c r="E27" t="n">
+        <v>45.4693</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Climbing</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Control/ELS</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0488</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.1457</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.7377</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Climbing</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Control/Resilient</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.2737</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.9731</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Climbing</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ELS/Resilient</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.0396</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.1378</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.8904</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.8904</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Climbing</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Experiment</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.1956</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0745</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-2.6239</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4.4057</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.1181</v>
+      </c>
+      <c r="E32" t="n">
+        <v>37.3104</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Control/ELS</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1212</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.7369</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Control/Resilient</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.0519</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.322</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.7475000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ELS/Resilient</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.0927</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.1726</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.5368000000000001</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.5914</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.828</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Experiment</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.0613</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.554</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.5795</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>significant</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Freeze</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Control/ELS</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.3416478079282853</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.08198848478430119</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-4.167021854680041</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>3.086049215065118e-05</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Freeze</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Control/Resilient</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0670186109510118</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1110629287165263</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6034291705206886</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5462232214655676</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Freeze</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ELS/Resilient</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.4086664188792971</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1176001401377532</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.475050441271564</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>0.0005107573006136</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sniff</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Control/ELS</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7122644066487785</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2476069428918566</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.876593032206948</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0.0040199367747777</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sniff</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Control/Resilient</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.363075390529554</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3138676536064639</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.156778617859068</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2473628198779007</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sniff</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ELS/Resilient</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.3491890161192245</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3124160673577382</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.117705049783431</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2636929853268198</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Groom</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Control/ELS</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0657920068416422</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4237538768871108</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1552599526049161</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8766163859000841</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Groom</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Control/Resilient</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1565270307442328</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5310732375744608</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.294737184383701</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.76819465525537</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Groom</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ELS/Resilient</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0907350239025905</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5918401476246433</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1533100183668792</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8781538005582127</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Control/ELS</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1407695611938317</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0340640495018712</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.132496378215362</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>3.588444230979757e-05</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Control/Resilient</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.0037471788166275</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.034077248792987</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.1099613070113432</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9124400613039352</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ELS/Resilient</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.1445167400104587</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0325680545474696</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-4.437377117500765</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>9.106167537030892e-06</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Locomotion</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Control/ELS</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.2426275308278193</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1615453482112258</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1.501915923388743</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1331188237189243</v>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Locomotion</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Control/Resilient</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0218368633282987</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.2551261072049063</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0855924294363192</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9317904168091666</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Locomotion</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ELS/Resilient</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.2644643941561181</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.2442338923042543</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.082832491678352</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2788827807889146</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Climb</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Control/ELS</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.0146566202937246</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.1494183646225211</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.09809115720649191</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.921859909190788</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Climb</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Control/Resilient</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0057322879042903</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.272052617366275</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0210705118729763</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.983189407787424</v>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Climb</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ELS/Resilient</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.0089243323894344</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.2872855372931595</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.0310643287981726</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.975218237426922</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Control/ELS</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.0267473249112214</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.1296989066103411</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.2062262945020755</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.8366141492357301</v>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Control/Resilient</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.0206137995032985</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1654846315888874</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.1245662470609918</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.900866951158532</v>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ELS/Resilient</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.0473611244145201</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.1788745472574913</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.2647728541632224</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.7911844500072999</v>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3401,7 +5019,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3917,7 +5535,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4343,531 +5961,1160 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="57" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>cluster</t>
+          <t>section</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>n_obs</t>
+          <t>claim</t>
         </is>
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
-          <t>n_animals</t>
+          <t>repo_source</t>
         </is>
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t>n_control</t>
+          <t>manuscript_beta</t>
         </is>
       </c>
       <c r="E1" s="6" t="inlineStr">
         <is>
-          <t>n_els</t>
+          <t>manuscript_se</t>
         </is>
       </c>
       <c r="F1" s="6" t="inlineStr">
         <is>
-          <t>const_beta</t>
+          <t>manuscript_z</t>
         </is>
       </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
-          <t>const_SE</t>
+          <t>manuscript_p</t>
         </is>
       </c>
       <c r="H1" s="6" t="inlineStr">
         <is>
-          <t>const_z</t>
+          <t>repo_beta</t>
         </is>
       </c>
       <c r="I1" s="6" t="inlineStr">
         <is>
-          <t>const_p</t>
+          <t>repo_se</t>
         </is>
       </c>
       <c r="J1" s="6" t="inlineStr">
         <is>
-          <t>stress_beta</t>
+          <t>repo_z</t>
         </is>
       </c>
       <c r="K1" s="6" t="inlineStr">
         <is>
-          <t>stress_SE</t>
+          <t>repo_p</t>
         </is>
       </c>
       <c r="L1" s="6" t="inlineStr">
         <is>
-          <t>stress_z</t>
+          <t>status</t>
         </is>
       </c>
       <c r="M1" s="6" t="inlineStr">
         <is>
-          <t>stress_p</t>
-        </is>
-      </c>
-      <c r="N1" s="6" t="inlineStr">
-        <is>
-          <t>exp_bin_beta</t>
-        </is>
-      </c>
-      <c r="O1" s="6" t="inlineStr">
-        <is>
-          <t>exp_bin_SE</t>
-        </is>
-      </c>
-      <c r="P1" s="6" t="inlineStr">
-        <is>
-          <t>exp_bin_z</t>
-        </is>
-      </c>
-      <c r="Q1" s="6" t="inlineStr">
-        <is>
-          <t>exp_bin_p</t>
-        </is>
-      </c>
-      <c r="R1" s="6" t="inlineStr">
-        <is>
-          <t>converged</t>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1230</v>
-      </c>
-      <c r="C2" t="n">
-        <v>82</v>
-      </c>
-      <c r="D2" t="n">
-        <v>41</v>
-      </c>
-      <c r="E2" t="n">
-        <v>41</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4.9801</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.0655</v>
-      </c>
-      <c r="H2" t="n">
-        <v>76.07470000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-0.2042</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.0813</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-2.5103</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.012062</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.3758</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.0796</v>
-      </c>
-      <c r="P2" t="n">
-        <v>4.7229</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2e-06</v>
-      </c>
-      <c r="R2" t="b">
-        <v>0</v>
+          <t>Figure 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Classifier validation r=0.95, R2=0.90, p&lt;0.001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>not present</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>not_reproducible_from_repo</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Manual validation frame-level table is not bundled; Figure 7 classifier metrics are separate.</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sniff</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1230</v>
-      </c>
-      <c r="C3" t="n">
-        <v>82</v>
+          <t>Figure 3A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Freeze ELS vs Control frequency</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>statistics/stats_figure3A_GEE.csv</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>41</v>
+        <v>-0.204</v>
       </c>
       <c r="E3" t="n">
-        <v>41</v>
+        <v>0.081</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6604</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.1923</v>
+        <v>-2.51</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.012</t>
+        </is>
       </c>
       <c r="H3" t="n">
-        <v>13.8322</v>
+        <v>-0.2041</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.0813</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6222</v>
+        <v>-2.5103</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2308</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2.6954</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.00703</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.9745</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.2384</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4.0875</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4.4e-05</v>
-      </c>
-      <c r="R3" t="b">
-        <v>0</v>
+        <v>0.0121</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Turn</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1230</v>
-      </c>
-      <c r="C4" t="n">
-        <v>82</v>
+          <t>Figure 3A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sniff ELS vs Control frequency</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>statistics/stats_figure3A_GEE.csv</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>41</v>
+        <v>0.621</v>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>0.231</v>
       </c>
       <c r="F4" t="n">
-        <v>5.7604</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.0285</v>
+        <v>2.694</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.007</t>
+        </is>
       </c>
       <c r="H4" t="n">
-        <v>202.1714</v>
+        <v>0.6228</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1005</v>
+        <v>2.6959</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0324</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3.0988</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.001943</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.0342</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.2486</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.8037029999999999</v>
-      </c>
-      <c r="R4" t="b">
-        <v>0</v>
+        <v>0.007</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>numeric_mismatch_same_conclusion</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Locomotion</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1230</v>
-      </c>
-      <c r="C5" t="n">
-        <v>82</v>
+          <t>Figure 3A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Turn ELS vs Control frequency</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>statistics/stats_figure3A_GEE.csv</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>41</v>
+        <v>0.101</v>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>0.032</v>
       </c>
       <c r="F5" t="n">
-        <v>3.9269</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.11</v>
+        <v>3.099</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
       </c>
       <c r="H5" t="n">
-        <v>35.7095</v>
+        <v>0.1005</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.0324</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1575</v>
+        <v>3.0988</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1604</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-0.9815</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.326349</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.8008</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.1849</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-4.3309</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.5e-05</v>
-      </c>
-      <c r="R5" t="b">
-        <v>1</v>
+        <v>0.0019</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Climb</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1230</v>
-      </c>
-      <c r="C6" t="n">
-        <v>82</v>
+          <t>Figure 4E</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Simpson diversity ELS vs Control</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>statistics/stats_figure4_diversity_MixedLM.csv</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>41</v>
+        <v>-0.013</v>
       </c>
       <c r="E6" t="n">
-        <v>41</v>
+        <v>0.007</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4271</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.0898</v>
+        <v>-1.915</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
       </c>
       <c r="H6" t="n">
-        <v>38.1471</v>
+        <v>-0.0134</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.0071</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0121</v>
+        <v>-1.8864</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1426</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.08459999999999999</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.932561</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-0.3743</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.1544</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-2.4238</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.015359</v>
-      </c>
-      <c r="R6" t="b">
-        <v>1</v>
+        <v>0.0592</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>minor_mismatch_same_interpretation</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Repo remains near-threshold and non-significant.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Groom</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1230</v>
-      </c>
-      <c r="C7" t="n">
-        <v>82</v>
+          <t>Figure 4H</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cumulative usage index ELS vs Control</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>statistics/stats_figure4_diversity_MixedLM.csv</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>41</v>
+        <v>0.064</v>
       </c>
       <c r="E7" t="n">
-        <v>41</v>
+        <v>0.028</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7385</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.2196</v>
+        <v>2.25</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.025</t>
+        </is>
       </c>
       <c r="H7" t="n">
-        <v>-3.3633</v>
+        <v>0.0636</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00077</v>
+        <v>0.0275</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0906</v>
+        <v>2.316</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3706</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.2446</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.806777</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-1.4186</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.436</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-3.2534</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.00114</v>
-      </c>
-      <c r="R7" t="b">
-        <v>1</v>
+        <v>0.0206</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>numeric_mismatch_same_conclusion</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jump</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1230</v>
-      </c>
-      <c r="C8" t="n">
-        <v>82</v>
+          <t>Figure 4K</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Freezing bout duration ELS vs Control</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>statistics/stats_figure4_bouts_MixedLM.csv</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>-0.094</v>
       </c>
       <c r="E8" t="n">
-        <v>41</v>
+        <v>0.033</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6663</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.08169999999999999</v>
+        <v>-2.824</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
       </c>
       <c r="H8" t="n">
-        <v>20.3868</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.0384</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0131</v>
+        <v>-2.4462</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1155</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.1135</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.909633</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-0.1386</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.1314</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-1.0553</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.291303</v>
-      </c>
-      <c r="R8" t="b">
-        <v>1</v>
+        <v>0.0144</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>numeric_mismatch_same_conclusion</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Repo remains significant but less strong than the manuscript value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Figure 4L</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sniffing bout duration ELS vs Control</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>statistics/stats_figure4_bouts_MixedLM.csv</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1274</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.5191</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>numeric_mismatch_same_conclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Figure 4N</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Turn bout duration ELS vs Control</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>statistics/stats_figure4_bouts_MixedLM.csv</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.824</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1638</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0608</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.6928</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>numeric_mismatch_same_conclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Figure 4U</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Recurrence ELS vs Control</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>statistics/stats_figure4_transition_MixedLM.csv</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.908</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.056</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>minor_mismatch_same_interpretation</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Repo remains near-threshold and non-significant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Figure 4V</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Determinism ELS vs Control</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>statistics/stats_figure4_transition_MixedLM.csv</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.030</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.1666</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Figure 4W</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Markov entropy ELS vs Control</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>statistics/stats_figure4_transition_MixedLM.csv</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.638</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.102</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.0412</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-1.618</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.1057</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>numeric_mismatch_same_conclusion</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Repo remains non-significant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Figure 5C</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Freeze resilient vs vulnerable ELS frequency</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>statistics/fig5c_frequency_gee.csv</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.476</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.4751</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>numeric_mismatch_same_conclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Figure 5C</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Turn resilient vs vulnerable ELS frequency</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>statistics/fig5c_frequency_gee.csv</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.145</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-4.437</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.1445</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-4.4374</v>
+      </c>
+      <c r="K15" t="n">
+        <v>9.109999999999999e-06</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Figure 5D</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Freeze time resilient vs vulnerable ELS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>statistics/fig5_timecourse_mixedlm.csv</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7.484</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2407</v>
+      </c>
+      <c r="J16" t="n">
+        <v>7.747</v>
+      </c>
+      <c r="K16" t="n">
+        <v>9.409999999999999e-15</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>numeric_mismatch_same_conclusion</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Repo coefficient and standard error are scaled per 30 s bin for the audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Figure 6G</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Simpson vulnerable ELS vs Control</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>statistics/fig6_diversity_resilience_stats.csv</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.022</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-2.835</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.022</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-2.8178</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>numeric_mismatch_same_conclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Figure 6M</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Freezing bout resilient vs vulnerable ELS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>statistics/fig6_bout_resilience_stats.csv</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.969</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.0885</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.9721</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>numeric_mismatch_same_conclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Figure 6W</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lempel-Ziv vulnerable ELS vs Control</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>statistics/fig6_transition_resilience_stats.csv</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-8.965</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.658</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>-8.965400000000001</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.4174</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-2.0296</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>major_mismatch</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Repo p-value is significant at 0.05 but does not support p&lt;0.001.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Figure 6X</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Recurrence vulnerable ELS vs Control</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>statistics/fig6_transition_resilience_stats.csv</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.798</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.0248</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>numeric_mismatch_same_conclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Figure 6X</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Recurrence resilient vs vulnerable ELS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>statistics/fig6_transition_resilience_stats.csv</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-2.727</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.0333</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-2.755</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>numeric_mismatch_same_conclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Figure 6Y</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Determinism vulnerable ELS vs Control</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>statistics/fig6_transition_resilience_stats.csv</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.7987</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>numeric_mismatch_same_conclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Figure 6Z</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Markov entropy vulnerable ELS vs Control</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>statistics/fig6_transition_resilience_stats.csv</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.046</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-2.1002</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>numeric_mismatch_same_conclusion</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4875,7 +7122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10191,7 +12438,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10991,309 +13238,6 @@
       </c>
       <c r="I22" t="n">
         <v>0.0836756124872735</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>cluster</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>parameter</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>coef</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>se</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>z</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>p_value</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>ci_low</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>ci_high</t>
-        </is>
-      </c>
-      <c r="I1" s="6" t="inlineStr">
-        <is>
-          <t>n_obs</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Freezing</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Condition[T.ELS]</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.09384744101836941</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.0383642587639759</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-2.446220624142284</v>
-      </c>
-      <c r="F2" s="7" t="n">
-        <v>0.0144362631038941</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-0.1690400064893374</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-0.0186548755474013</v>
-      </c>
-      <c r="I2" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Sniffing</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Condition[T.ELS]</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.32087940229676</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.1273798012950552</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2.519076015462558</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>0.0117663251497295</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.07121957940058329</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.5705392251929368</v>
-      </c>
-      <c r="I3" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Grooming</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Condition[T.ELS]</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0004458041958041</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.0014229031856538</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.3133060634756585</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.7540481438919768</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.0023430348015646</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0032346431931729</v>
-      </c>
-      <c r="I4" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Turn</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Condition[T.ELS]</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.1638237031004309</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.0608374398867533</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2.692810601586503</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>0.0070852505618133</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.0445845120107738</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.2830628941900879</v>
-      </c>
-      <c r="I5" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Locomotion</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Condition[T.ELS]</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0021834686706813</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.0050214250457611</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.4348304815431917</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.6636854779360024</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.0076583435700779</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0120252809114406</v>
-      </c>
-      <c r="I6" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Climbing</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Condition[T.ELS]</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.0068716770819006</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.0251307636769246</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.2734368589129003</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.7845174226157636</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.0561270687926603</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0423837146288589</v>
-      </c>
-      <c r="I7" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Jump</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Condition[T.ELS]</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.0198902133924089</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.0404043848528515</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0.4922785847339841</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.6225224170797505</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-0.09908135252149371</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.0593009257366757</v>
-      </c>
-      <c r="I8" t="n">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -12729,6 +14673,309 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>coef</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>ci_low</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>ci_high</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>n_obs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Freezing</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Condition[T.ELS]</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.09384744101836941</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0383642587639759</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-2.446220624142284</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>0.0144362631038941</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.1690400064893374</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.0186548755474013</v>
+      </c>
+      <c r="I2" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sniffing</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Condition[T.ELS]</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.32087940229676</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1273798012950552</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.519076015462558</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>0.0117663251497295</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.07121957940058329</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5705392251929368</v>
+      </c>
+      <c r="I3" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Grooming</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Condition[T.ELS]</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0004458041958041</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0014229031856538</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3133060634756585</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7540481438919768</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.0023430348015646</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0032346431931729</v>
+      </c>
+      <c r="I4" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Condition[T.ELS]</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.1638237031004309</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0608374398867533</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.692810601586503</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>0.0070852505618133</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0445845120107738</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2830628941900879</v>
+      </c>
+      <c r="I5" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Locomotion</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Condition[T.ELS]</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0021834686706813</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0050214250457611</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.4348304815431917</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6636854779360024</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.0076583435700779</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0120252809114406</v>
+      </c>
+      <c r="I6" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Climbing</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Condition[T.ELS]</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.0068716770819006</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0251307636769246</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.2734368589129003</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.7845174226157636</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.0561270687926603</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0423837146288589</v>
+      </c>
+      <c r="I7" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Condition[T.ELS]</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.0198902133924089</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0404043848528515</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.4922785847339841</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6225224170797505</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.09908135252149371</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0593009257366757</v>
+      </c>
+      <c r="I8" t="n">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12919,582 +15166,6 @@
         <v>0.1175074139319955</v>
       </c>
       <c r="I5" t="n">
-        <v>82</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>figure</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>parameter</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>coef</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>se</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>p_value</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>ci_low</t>
-        </is>
-      </c>
-      <c r="I1" s="6" t="inlineStr">
-        <is>
-          <t>ci_high</t>
-        </is>
-      </c>
-      <c r="J1" s="6" t="inlineStr">
-        <is>
-          <t>r_squared</t>
-        </is>
-      </c>
-      <c r="K1" s="6" t="inlineStr">
-        <is>
-          <t>n_obs</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>4E</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>simpson</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0.7114633069955248</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.008757538834209299</v>
-      </c>
-      <c r="F2" t="n">
-        <v>81.24009729952401</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>6.832184336524686e-78</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.6940318619818744</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.7288947520091753</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.0642816230621885</v>
-      </c>
-      <c r="K2" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>4E</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>simpson</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>C(group, Treatment('Control'))[T.ELS]</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>-0.0134408686098249</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.0075861775275381</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-1.77175772133383</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.0802908672847962</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-0.0285407772643563</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.0016590400447064</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.0642816230621885</v>
-      </c>
-      <c r="K3" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>4E</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>simpson</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Experiment</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>-0.0058808971765059</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0038879159828633</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-1.512609120780121</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.1343693130941072</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-0.0136196003619534</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.0018578060089415</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.0642816230621885</v>
-      </c>
-      <c r="K4" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4E</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>shannon</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1.454481413632885</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.0222923412925677</v>
-      </c>
-      <c r="F5" t="n">
-        <v>65.24578977793642</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>1.765377536515339e-70</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.410109618220572</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.498853209045198</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.0849344162794882</v>
-      </c>
-      <c r="K5" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>4E</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>shannon</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>C(group, Treatment('Control'))[T.ELS]</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>-0.0115738864285025</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.0193106375833909</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.5993528892312301</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.5506526332013592</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.050010749066041</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.0268629762090358</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.0849344162794882</v>
-      </c>
-      <c r="K6" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>4E</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>shannon</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Experiment</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>-0.026134387950471</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.009896701761488</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-2.640716935835144</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>0.0099672396745093</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.0458332800522097</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.0064354958487322</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.0849344162794882</v>
-      </c>
-      <c r="K7" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>4E</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>evenness</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.7046230394190305</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.0120326377077488</v>
-      </c>
-      <c r="F8" t="n">
-        <v>58.55931646352694</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>7.621573069444798e-67</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.6806726731640189</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.7285734056740421</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.0103907346839928</v>
-      </c>
-      <c r="K8" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>4E</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>evenness</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>C(group, Treatment('Control'))[T.ELS]</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>-0.0064970651245983</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.0104232167854011</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-0.6233262972807261</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.5348656252814696</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.0272439591663742</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0142498289171774</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.0103907346839928</v>
-      </c>
-      <c r="K9" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>4E</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>evenness</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Experiment</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.0035472432979535</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.0053418986025181</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-0.6640416754225488</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.5085970973373826</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.0141800264943638</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.0070855398984567</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.0103907346839928</v>
-      </c>
-      <c r="K10" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>4E</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>cui</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.1018409439905418</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.0333383664192781</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3.054767072559728</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>0.0030702759675753</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0354825855425605</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.168199302438523</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.3056412614185464</v>
-      </c>
-      <c r="K11" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>4E</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>cui</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>C(group, Treatment('Control'))[T.ELS]</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.0636457878443564</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.0288792057817458</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2.203862125757839</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>0.030445442604596</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.0061631666248013</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.1211284090639115</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.3056412614185464</v>
-      </c>
-      <c r="K12" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>4E</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>cui</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Experiment</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.08095401215251111</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.0148005929631449</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5.46964654416854</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>5.130355535546745e-07</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.0514941687774887</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.1104138555275336</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.3056412614185464</v>
-      </c>
-      <c r="K13" t="n">
         <v>82</v>
       </c>
     </row>
@@ -17537,6 +19208,538 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>n_obs</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>n_animals</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>n_control</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>n_els</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>const_beta</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>const_SE</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>const_z</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>const_p</t>
+        </is>
+      </c>
+      <c r="J1" s="6" t="inlineStr">
+        <is>
+          <t>stress_beta</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>stress_SE</t>
+        </is>
+      </c>
+      <c r="L1" s="6" t="inlineStr">
+        <is>
+          <t>stress_z</t>
+        </is>
+      </c>
+      <c r="M1" s="6" t="inlineStr">
+        <is>
+          <t>stress_p</t>
+        </is>
+      </c>
+      <c r="N1" s="6" t="inlineStr">
+        <is>
+          <t>exp_bin_beta</t>
+        </is>
+      </c>
+      <c r="O1" s="6" t="inlineStr">
+        <is>
+          <t>exp_bin_SE</t>
+        </is>
+      </c>
+      <c r="P1" s="6" t="inlineStr">
+        <is>
+          <t>exp_bin_z</t>
+        </is>
+      </c>
+      <c r="Q1" s="6" t="inlineStr">
+        <is>
+          <t>exp_bin_p</t>
+        </is>
+      </c>
+      <c r="R1" s="6" t="inlineStr">
+        <is>
+          <t>converged</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Freeze</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1230</v>
+      </c>
+      <c r="C2" t="n">
+        <v>82</v>
+      </c>
+      <c r="D2" t="n">
+        <v>41</v>
+      </c>
+      <c r="E2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.9801</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="H2" t="n">
+        <v>76.07470000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-0.2042</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0813</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-2.5103</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.012062</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0796</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.7229</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sniff</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1230</v>
+      </c>
+      <c r="C3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D3" t="n">
+        <v>41</v>
+      </c>
+      <c r="E3" t="n">
+        <v>41</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.6604</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1923</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13.8322</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6222</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.6954</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.00703</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.9745</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.2384</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.0875</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.4e-05</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Turn</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1230</v>
+      </c>
+      <c r="C4" t="n">
+        <v>82</v>
+      </c>
+      <c r="D4" t="n">
+        <v>41</v>
+      </c>
+      <c r="E4" t="n">
+        <v>41</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5.7604</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="H4" t="n">
+        <v>202.1714</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0324</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3.0988</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.001943</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0342</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2486</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.8037029999999999</v>
+      </c>
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Locomotion</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1230</v>
+      </c>
+      <c r="C5" t="n">
+        <v>82</v>
+      </c>
+      <c r="D5" t="n">
+        <v>41</v>
+      </c>
+      <c r="E5" t="n">
+        <v>41</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.9269</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H5" t="n">
+        <v>35.7095</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.1575</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.9815</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.326349</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.8008</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1849</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-4.3309</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="R5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Climb</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1230</v>
+      </c>
+      <c r="C6" t="n">
+        <v>82</v>
+      </c>
+      <c r="D6" t="n">
+        <v>41</v>
+      </c>
+      <c r="E6" t="n">
+        <v>41</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.4271</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="H6" t="n">
+        <v>38.1471</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.08459999999999999</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.932561</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.3743</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1544</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-2.4238</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.015359</v>
+      </c>
+      <c r="R6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Groom</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1230</v>
+      </c>
+      <c r="C7" t="n">
+        <v>82</v>
+      </c>
+      <c r="D7" t="n">
+        <v>41</v>
+      </c>
+      <c r="E7" t="n">
+        <v>41</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.7385</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2196</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-3.3633</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.00077</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2446</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.806777</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-1.4186</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-3.2534</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.00114</v>
+      </c>
+      <c r="R7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jump</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1230</v>
+      </c>
+      <c r="C8" t="n">
+        <v>82</v>
+      </c>
+      <c r="D8" t="n">
+        <v>41</v>
+      </c>
+      <c r="E8" t="n">
+        <v>41</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.6663</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.08169999999999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>20.3868</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1155</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.909633</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.1386</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-1.0553</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.291303</v>
+      </c>
+      <c r="R8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -28856,7 +31059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30210,7 +32413,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32572,7 +34775,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34680,1634 +36883,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G57"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="57" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>cluster</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>panel</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>parameter</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>coef</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>se</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>z</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1.167734739514446e-19</v>
-      </c>
-      <c r="E2" t="n">
-        <v>57937066.35940005</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2.015522726454005e-27</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.Control]</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1.983764337921433e-18</v>
-      </c>
-      <c r="E3" t="n">
-        <v>47222751.81826599</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4.200865602995425e-26</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1.59747688188722e-17</v>
-      </c>
-      <c r="E4" t="n">
-        <v>96124105.99966487</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.661889975749464e-25</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>C(experiment)[T.3]</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>5.430008571821657e-20</v>
-      </c>
-      <c r="E5" t="n">
-        <v>54258354.96999358</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.00076911193209e-27</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.0847285166940339</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.0043413334057078</v>
-      </c>
-      <c r="F6" t="n">
-        <v>19.51670345858133</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>7.918530004551611e-85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.Control]:time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.0415235158262912</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.005672574805247</v>
-      </c>
-      <c r="F7" t="n">
-        <v>7.320047289263159</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>2.478835867593613e-13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]:time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.0621669859514687</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.008024619437083</v>
-      </c>
-      <c r="F8" t="n">
-        <v>7.747032297156085</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>9.406503761765563e-15</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Freeze</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Group Var</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sniff</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>-3.578632558552098e-20</v>
-      </c>
-      <c r="E10" t="n">
-        <v>30711290.43649872</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-1.165249817799608e-27</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sniff</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.Control]</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>5.568326604626117e-18</v>
-      </c>
-      <c r="E11" t="n">
-        <v>47691063.63991545</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.167582808944873e-25</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sniff</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>6.617483125559545e-18</v>
-      </c>
-      <c r="E12" t="n">
-        <v>69970892.32654329</v>
-      </c>
-      <c r="F12" t="n">
-        <v>9.457479968494296e-26</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sniff</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>C(experiment)[T.3]</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>-9.98932096343714e-21</v>
-      </c>
-      <c r="E13" t="n">
-        <v>18092547.81131582</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-5.521235078450038e-28</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sniff</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>-0.0253902572523262</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.0030708557776315</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-8.268137317705328</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>1.360681196832254e-16</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Sniff</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.Control]:time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.0171463548133018</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.0040125135498317</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4.273220414176795</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>1.92669829275846e-05</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sniff</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]:time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.0112817916438606</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.0056762396846234</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.987546733521882</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>0.0468618424244712</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sniff</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Group Var</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Groom</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>8.730431564512796e-23</v>
-      </c>
-      <c r="E18" t="n">
-        <v>578778.7694682108</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1.508422911319713e-28</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Groom</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.Control]</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>-3.303675330007019e-20</v>
-      </c>
-      <c r="E19" t="n">
-        <v>799094.3650951521</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-4.134274341446063e-26</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Groom</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>-8.402347656431446e-20</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2030758.645158524</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-4.137541246697757e-26</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Groom</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>C(experiment)[T.3]</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>-1.289751086399553e-23</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1231877.14494184</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-1.046980286707442e-29</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Groom</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>5.911330049261086e-05</v>
-      </c>
-      <c r="E22" t="n">
-        <v>9.018022514846688e-05</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.6555018064691073</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.5121447237052608</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Groom</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.Control]:time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>-8.698786495254115e-05</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.0001178333993966</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-0.7382275772231575</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.4603761675161169</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Groom</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]:time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>-0.0002297482211275</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.0001666911798608</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-1.378286609521128</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.1681148158077938</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Groom</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Group Var</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Turn</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>6.407143061156887e-21</v>
-      </c>
-      <c r="E26" t="n">
-        <v>54965824.70530519</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1.165659406641902e-28</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Turn</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.Control]</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>-9.767338664955905e-18</v>
-      </c>
-      <c r="E27" t="n">
-        <v>90584380.01758012</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-1.078258598564158e-25</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Turn</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>-2.019034610743105e-17</v>
-      </c>
-      <c r="E28" t="n">
-        <v>121906486.7650236</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-1.656215894921836e-25</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Turn</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>C(experiment)[T.3]</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>-9.027860363729511e-21</v>
-      </c>
-      <c r="E29" t="n">
-        <v>85757026.40332018</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-1.052725443308979e-28</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Turn</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0.0036431308155446</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.0056886486120862</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.6404211375974876</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.5218988444059371</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Turn</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.Control]:time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>-0.0413771610129894</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.007433035378116</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-5.56665734900303</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>2.596723010716253e-08</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Turn</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]:time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>-0.0540584747308885</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.0105150275174129</v>
-      </c>
-      <c r="F32" t="n">
-        <v>-5.1410683083204</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>2.731807052640286e-07</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Turn</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Group Var</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Locomotion</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>-2.563198223044489e-20</v>
-      </c>
-      <c r="E34" t="n">
-        <v>20149826.89930953</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-1.272069599333542e-27</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Locomotion</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.Control]</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>5.948582117017596e-19</v>
-      </c>
-      <c r="E35" t="n">
-        <v>26827188.95559184</v>
-      </c>
-      <c r="F35" t="n">
-        <v>2.217370640980884e-26</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Locomotion</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>-6.59350385538885e-20</v>
-      </c>
-      <c r="E36" t="n">
-        <v>39407904.2365334</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-1.673142478172258e-27</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Locomotion</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>C(experiment)[T.3]</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>-1.002492387846058e-20</v>
-      </c>
-      <c r="E37" t="n">
-        <v>21438700.53821893</v>
-      </c>
-      <c r="F37" t="n">
-        <v>-4.676087461825903e-28</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Locomotion</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>-0.0184532019704433</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.0017401956340854</v>
-      </c>
-      <c r="F38" t="n">
-        <v>-10.60409623435292</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>2.852080397105039e-26</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Locomotion</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.Control]:time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>-0.0064833059660645</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.0022738152055162</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-2.851289739964851</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>0.0043542272933309</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Locomotion</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]:time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>-0.0034568509396095</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.0032166172013532</v>
-      </c>
-      <c r="F40" t="n">
-        <v>-1.074685212202201</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.2825156866283029</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Locomotion</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Group Var</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Climb</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>6.949261310959979</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.5821771162369743</v>
-      </c>
-      <c r="F42" t="n">
-        <v>11.93667891977275</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>7.620559102456307e-33</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Climb</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.Control]</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>0.4525802160234881</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.7283750981233754</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.6213559705562971</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.534365434848195</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Climb</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>-0.0131287063642658</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1.03270070912007</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-0.0127129828113049</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.9898567805182504</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Climb</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>C(experiment)[T.3]</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>-1.282080024006236</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.4894079502557587</v>
-      </c>
-      <c r="F45" t="n">
-        <v>-2.619655081892797</v>
-      </c>
-      <c r="G45" s="7" t="n">
-        <v>0.0088018741711899</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Climb</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>-0.0132233169129719</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.0018502951375046</v>
-      </c>
-      <c r="F46" t="n">
-        <v>-7.146598747919252</v>
-      </c>
-      <c r="G46" s="7" t="n">
-        <v>8.895440574442136e-13</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Climb</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.Control]:time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>-0.0024445111938805</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.0024176759991481</v>
-      </c>
-      <c r="F47" t="n">
-        <v>-1.011099582715724</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.3119687700804534</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Climb</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]:time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>-0.0004287994891444</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.0034201276283545</v>
-      </c>
-      <c r="F48" t="n">
-        <v>-0.125375288801941</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.9002264504128519</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Climb</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Group Var</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>0.118172825197827</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.0266040885179105</v>
-      </c>
-      <c r="F49" t="n">
-        <v>4.44190467635342</v>
-      </c>
-      <c r="G49" s="7" t="n">
-        <v>8.916606238198319e-06</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Jump</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>2.873196023389088e-21</v>
-      </c>
-      <c r="E50" t="n">
-        <v>5999080.844399334</v>
-      </c>
-      <c r="F50" t="n">
-        <v>4.789393738661594e-28</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Jump</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.Control]</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>-2.541163907958393e-19</v>
-      </c>
-      <c r="E51" t="n">
-        <v>6017900.438476866</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-4.222675223589379e-26</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Jump</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>-2.777725951462236e-19</v>
-      </c>
-      <c r="E52" t="n">
-        <v>5666649.246303425</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-4.901884395393369e-26</v>
-      </c>
-      <c r="G52" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Jump</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>C(experiment)[T.3]</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>9.550301325054638e-22</v>
-      </c>
-      <c r="E53" t="n">
-        <v>6274587.774688235</v>
-      </c>
-      <c r="F53" t="n">
-        <v>1.522060359659111e-28</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Jump</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>0.0020530925013683</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.0004566247318219</v>
-      </c>
-      <c r="F54" t="n">
-        <v>4.496235876616957</v>
-      </c>
-      <c r="G54" s="7" t="n">
-        <v>6.91670039181544e-06</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Jump</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.Control]:time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>-0.0002791861908766</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.0005966457093067</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-0.4679262525847488</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.6398373289510549</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Jump</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>C(group_ext, Treatment('ELS'))[T.ELS resilient]:time_bin_numeric</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>-0.0003163200145958</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.000844035543</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-0.3747709645870242</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.7078308099381875</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Jump</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Group Var</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>